--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_69_R7.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_69_R7.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.423999999999999</v>
+        <v>8.599500000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>6.9194</v>
+        <v>6.9941</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5046</v>
+        <v>1.6054</v>
       </c>
       <c r="G2" t="n">
         <v>7.2128</v>
@@ -610,13 +610,13 @@
         <v>1.8556</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.1805</v>
+        <v>-0.005</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.2592</v>
+        <v>-0.1845</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0786</v>
+        <v>0.1795</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.2374</v>
+        <v>5.4459</v>
       </c>
       <c r="E3" t="n">
-        <v>4.1746</v>
+        <v>4.0133</v>
       </c>
       <c r="F3" t="n">
-        <v>1.0629</v>
+        <v>1.4325</v>
       </c>
       <c r="G3" t="n">
         <v>3.6451</v>
@@ -688,13 +688,13 @@
         <v>1.3917</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1937</v>
+        <v>0.0147</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0395</v>
+        <v>-0.1217</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2333</v>
+        <v>0.1364</v>
       </c>
       <c r="V3" t="n">
         <v>0.3943</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8192</v>
+        <v>2.324</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8954</v>
+        <v>2.1313</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0762</v>
+        <v>0.1927</v>
       </c>
       <c r="G4" t="n">
         <v>2.0855</v>
@@ -766,13 +766,13 @@
         <v>1.1598</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9647</v>
+        <v>-0.4599</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.8215</v>
+        <v>-0.5856</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1432</v>
+        <v>0.1256</v>
       </c>
       <c r="V4" t="n">
         <v>0.9304</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. BRYANT</t>
+          <t>I. WAINRIGHT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2718</v>
+        <v>1.8864</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6633</v>
+        <v>1.4041</v>
       </c>
       <c r="F5" t="n">
-        <v>1.9351</v>
+        <v>0.4823</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1206</v>
+        <v>2.5809</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3313</v>
+        <v>0.657</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2108</v>
+        <v>1.9239</v>
       </c>
       <c r="J5" t="n">
-        <v>1.2324</v>
+        <v>3.3786</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9649</v>
+        <v>1.3444</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2676</v>
+        <v>2.0342</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.1119</v>
+        <v>-0.7977</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.6335</v>
+        <v>-0.6874</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4783</v>
+        <v>-0.1103</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9278</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.7834</v>
+        <v>-1.3917</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8556</v>
+        <v>1.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>1.0069</v>
+        <v>-0.1584</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1845</v>
+        <v>-0.1885</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1914</v>
+        <v>0.0301</v>
       </c>
       <c r="V5" t="n">
-        <v>1.0722</v>
+        <v>-0.5361</v>
       </c>
       <c r="W5" t="n">
-        <v>1.0722</v>
+        <v>-0.3943</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. WAINRIGHT</t>
+          <t>E. BRYANT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8688</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6217</v>
+        <v>-0.5453</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2471</v>
+        <v>1.1286</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5809</v>
+        <v>0.1206</v>
       </c>
       <c r="H6" t="n">
-        <v>0.657</v>
+        <v>0.3313</v>
       </c>
       <c r="I6" t="n">
-        <v>1.9239</v>
+        <v>-0.2108</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3786</v>
+        <v>1.2324</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3444</v>
+        <v>0.9649</v>
       </c>
       <c r="L6" t="n">
-        <v>2.0342</v>
+        <v>0.2676</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.7977</v>
+        <v>-1.1119</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.6874</v>
+        <v>-0.6335</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1103</v>
+        <v>-0.4783</v>
       </c>
       <c r="P6" t="n">
+        <v>-0.9278</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-2.7834</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.8556</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-0.06660000000000001</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.3848</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.0722</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.0722</v>
+      </c>
+      <c r="X6" t="n">
         <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>-1.3917</v>
-      </c>
-      <c r="R6" t="n">
-        <v>1.3917</v>
-      </c>
-      <c r="S6" t="n">
-        <v>-1.176</v>
-      </c>
-      <c r="T6" t="n">
-        <v>-0.9709</v>
-      </c>
-      <c r="U6" t="n">
-        <v>-0.2051</v>
-      </c>
-      <c r="V6" t="n">
-        <v>-0.5361</v>
-      </c>
-      <c r="W6" t="n">
-        <v>-0.3943</v>
-      </c>
-      <c r="X6" t="n">
-        <v>-0.1418</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.65</v>
+        <v>-0.0906</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.0985</v>
+        <v>-0.5703</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7485000000000001</v>
+        <v>0.4796</v>
       </c>
       <c r="G7" t="n">
         <v>-0.9387</v>
@@ -1000,13 +1000,13 @@
         <v>0.9278</v>
       </c>
       <c r="S7" t="n">
-        <v>1.0552</v>
+        <v>0.3145</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4876</v>
+        <v>0.0158</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5676</v>
+        <v>0.2987</v>
       </c>
       <c r="V7" t="n">
         <v>-0.3943</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5004999999999999</v>
+        <v>-0.5842000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.5536</v>
+        <v>-0.4356</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0531</v>
+        <v>-0.1485</v>
       </c>
       <c r="G8" t="n">
         <v>1.4412</v>
@@ -1078,13 +1078,13 @@
         <v>1.6237</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3154</v>
+        <v>-0.3991</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8215</v>
+        <v>-0.7035</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5061</v>
+        <v>0.3044</v>
       </c>
       <c r="V8" t="n">
         <v>-0.9304</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. OTURU</t>
+          <t>V. MICIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6204</v>
+        <v>-0.6717</v>
       </c>
       <c r="E9" t="n">
-        <v>1.0111</v>
+        <v>-0.5066000000000001</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6315</v>
+        <v>-0.1651</v>
       </c>
       <c r="G9" t="n">
-        <v>1.6824</v>
+        <v>-3.4456</v>
       </c>
       <c r="H9" t="n">
-        <v>1.9399</v>
+        <v>0.8609</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2575</v>
+        <v>-4.3064</v>
       </c>
       <c r="J9" t="n">
-        <v>2.9838</v>
+        <v>-1.8404</v>
       </c>
       <c r="K9" t="n">
-        <v>2.763</v>
+        <v>1.5159</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2208</v>
+        <v>-3.3563</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3015</v>
+        <v>-1.6052</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8231000000000001</v>
+        <v>-0.6551</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4783</v>
+        <v>-0.9500999999999999</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1598</v>
+        <v>0.4639</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.7834</v>
+        <v>-1.6237</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6237</v>
+        <v>2.0876</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7178</v>
+        <v>-0.3705</v>
       </c>
       <c r="T9" t="n">
-        <v>0.5272</v>
+        <v>-0.2592</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1907</v>
+        <v>-0.1114</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.8608</v>
+        <v>2.6805</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2836</v>
+        <v>3.2166</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.1444</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V. MICIC</t>
+          <t>D. OTURU</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1161</v>
+        <v>-1.0847</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.5813</v>
+        <v>0.614</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5348000000000001</v>
+        <v>-1.6988</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.4456</v>
+        <v>1.6824</v>
       </c>
       <c r="H10" t="n">
-        <v>0.8609</v>
+        <v>1.9399</v>
       </c>
       <c r="I10" t="n">
-        <v>-4.3064</v>
+        <v>-0.2575</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.8404</v>
+        <v>2.9838</v>
       </c>
       <c r="K10" t="n">
-        <v>1.5159</v>
+        <v>2.763</v>
       </c>
       <c r="L10" t="n">
-        <v>-3.3563</v>
+        <v>0.2208</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6052</v>
+        <v>-1.3015</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6551</v>
+        <v>-0.8231000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9500999999999999</v>
+        <v>-0.4783</v>
       </c>
       <c r="P10" t="n">
-        <v>0.4639</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.6237</v>
+        <v>-2.7834</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0876</v>
+        <v>1.6237</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8149</v>
+        <v>0.2535</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3339</v>
+        <v>0.13</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.481</v>
+        <v>0.1235</v>
       </c>
       <c r="V10" t="n">
-        <v>2.6805</v>
+        <v>-1.8608</v>
       </c>
       <c r="W10" t="n">
-        <v>3.2166</v>
+        <v>0.2836</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5361</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="11">
@@ -1267,19 +1267,19 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>16.0342</v>
+        <v>16.4078</v>
       </c>
       <c r="E11" t="n">
-        <v>12.7255</v>
+        <v>13.099</v>
       </c>
       <c r="F11" t="n">
-        <v>3.3088</v>
+        <v>3.3087</v>
       </c>
       <c r="G11" t="n">
         <v>14.3842</v>
       </c>
       <c r="H11" t="n">
-        <v>7.0233</v>
+        <v>7.023299999999999</v>
       </c>
       <c r="I11" t="n">
         <v>7.361000000000001</v>
@@ -1294,7 +1294,7 @@
         <v>11.0742</v>
       </c>
       <c r="M11" t="n">
-        <v>-7.3659</v>
+        <v>-7.365899999999999</v>
       </c>
       <c r="N11" t="n">
         <v>-3.6525</v>
@@ -1312,13 +1312,13 @@
         <v>13.9172</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.8653000000000001</v>
+        <v>-0.4918999999999999</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.3372</v>
+        <v>-1.9638</v>
       </c>
       <c r="U11" t="n">
-        <v>1.4718</v>
+        <v>1.4716</v>
       </c>
       <c r="V11" t="n">
         <v>1.3558</v>
@@ -1327,13 +1327,13 @@
         <v>6.07</v>
       </c>
       <c r="X11" t="n">
-        <v>-4.714200000000001</v>
+        <v>-4.7142</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>T. JONES</t>
+          <t>S. BROWN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.3212</v>
+        <v>0.2199</v>
       </c>
       <c r="E12" t="n">
-        <v>2.4831</v>
+        <v>0.6069</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.1619</v>
+        <v>-0.387</v>
       </c>
       <c r="G12" t="n">
-        <v>0.432</v>
+        <v>-0.9126</v>
       </c>
       <c r="H12" t="n">
-        <v>1.3888</v>
+        <v>-2.736</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9568</v>
+        <v>1.8234</v>
       </c>
       <c r="J12" t="n">
-        <v>2.7517</v>
+        <v>2.069</v>
       </c>
       <c r="K12" t="n">
-        <v>2.4941</v>
+        <v>-0.6009</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2576</v>
+        <v>2.6698</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.3198</v>
+        <v>-2.9816</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.1053</v>
+        <v>-2.1352</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.2144</v>
+        <v>-0.8464</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.6959</v>
+        <v>0.6959</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.3195</v>
+        <v>-1.3917</v>
       </c>
       <c r="R12" t="n">
-        <v>1.6237</v>
+        <v>2.0876</v>
       </c>
       <c r="S12" t="n">
-        <v>2.768</v>
+        <v>0.0424</v>
       </c>
       <c r="T12" t="n">
-        <v>1.0895</v>
+        <v>-0.0703</v>
       </c>
       <c r="U12" t="n">
-        <v>1.6786</v>
+        <v>0.1127</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.1829</v>
+        <v>0.3943</v>
       </c>
       <c r="W12" t="n">
-        <v>0.9615</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.1444</v>
+        <v>0.3943</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>S. BROWN</t>
+          <t>I. BONGA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.0153</v>
+        <v>-0.1504</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6069</v>
+        <v>1.2416</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.6223</v>
+        <v>-1.392</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.9126</v>
+        <v>-2.4038</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.736</v>
+        <v>-0.9182</v>
       </c>
       <c r="I13" t="n">
-        <v>1.8234</v>
+        <v>-1.4855</v>
       </c>
       <c r="J13" t="n">
-        <v>2.069</v>
+        <v>0.6919999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.6009</v>
+        <v>1.3311</v>
       </c>
       <c r="L13" t="n">
-        <v>2.6698</v>
+        <v>-0.6391</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.9816</v>
+        <v>-3.0957</v>
       </c>
       <c r="N13" t="n">
-        <v>-2.1352</v>
+        <v>-2.2493</v>
       </c>
       <c r="O13" t="n">
         <v>-0.8464</v>
       </c>
       <c r="P13" t="n">
-        <v>0.6959</v>
+        <v>1.6237</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.3917</v>
+        <v>-0.232</v>
       </c>
       <c r="R13" t="n">
-        <v>2.0876</v>
+        <v>1.8556</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1929</v>
+        <v>-0.3007</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.0703</v>
+        <v>-0.2906</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.1226</v>
+        <v>-0.0101</v>
       </c>
       <c r="V13" t="n">
-        <v>0.3943</v>
+        <v>0.9304</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X13" t="n">
-        <v>0.3943</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I. BONGA</t>
+          <t>T. JONES</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.3356</v>
+        <v>-0.1937</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1236</v>
+        <v>1.5395</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.4592</v>
+        <v>-1.7332</v>
       </c>
       <c r="G14" t="n">
-        <v>-2.4038</v>
+        <v>0.432</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.9182</v>
+        <v>1.3888</v>
       </c>
       <c r="I14" t="n">
-        <v>-1.4855</v>
+        <v>-0.9568</v>
       </c>
       <c r="J14" t="n">
-        <v>0.6919999999999999</v>
+        <v>2.7517</v>
       </c>
       <c r="K14" t="n">
-        <v>1.3311</v>
+        <v>2.4941</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.6391</v>
+        <v>0.2576</v>
       </c>
       <c r="M14" t="n">
-        <v>-3.0957</v>
+        <v>-2.3198</v>
       </c>
       <c r="N14" t="n">
-        <v>-2.2493</v>
+        <v>-1.1053</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.8464</v>
+        <v>-1.2144</v>
       </c>
       <c r="P14" t="n">
+        <v>-0.6959</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-2.3195</v>
+      </c>
+      <c r="R14" t="n">
         <v>1.6237</v>
       </c>
-      <c r="Q14" t="n">
-        <v>-0.232</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.8556</v>
-      </c>
       <c r="S14" t="n">
-        <v>-0.4859</v>
+        <v>1.2531</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4086</v>
+        <v>0.1458</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.07729999999999999</v>
+        <v>1.1073</v>
       </c>
       <c r="V14" t="n">
-        <v>0.9304</v>
+        <v>-1.1829</v>
       </c>
       <c r="W14" t="n">
-        <v>1.0722</v>
+        <v>0.9615</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1418</v>
+        <v>-2.1444</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.9360000000000001</v>
+        <v>-0.9867</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1615</v>
+        <v>1.0436</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.0975</v>
+        <v>-2.0303</v>
       </c>
       <c r="G15" t="n">
         <v>0.1528</v>
@@ -1624,13 +1624,13 @@
         <v>0.6959</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0887</v>
+        <v>-0.1395</v>
       </c>
       <c r="T15" t="n">
-        <v>0.3383</v>
+        <v>0.2203</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.427</v>
+        <v>-0.3598</v>
       </c>
       <c r="V15" t="n">
         <v>-0.5361</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>B. FERNANDO</t>
+          <t>A. LAKIC</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.6666</v>
+        <v>-1.9434</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.6766</v>
+        <v>-1.1048</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.9901</v>
+        <v>-0.8386</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.7766</v>
+        <v>-1.5218</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8127</v>
+        <v>1.0781</v>
       </c>
       <c r="I16" t="n">
-        <v>-1.5893</v>
+        <v>-2.5998</v>
       </c>
       <c r="J16" t="n">
-        <v>0.6885</v>
+        <v>-0.582</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5412</v>
+        <v>0.8066</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1472</v>
+        <v>-1.3887</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.4651</v>
+        <v>-0.9398</v>
       </c>
       <c r="N16" t="n">
         <v>0.2714</v>
       </c>
       <c r="O16" t="n">
-        <v>-1.7365</v>
+        <v>-1.2112</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.5515</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9278</v>
+        <v>0.6959</v>
       </c>
       <c r="S16" t="n">
-        <v>0.7336</v>
+        <v>-0.0452</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1142</v>
+        <v>-0.5228</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6194</v>
+        <v>0.4775</v>
       </c>
       <c r="V16" t="n">
+        <v>-1.0722</v>
+      </c>
+      <c r="W16" t="n">
         <v>0</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.0722</v>
       </c>
       <c r="X16" t="n">
         <v>-1.0722</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. LAKIC</t>
+          <t>D. WASHINGTON</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.2794</v>
+        <v>-1.9642</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.1048</v>
+        <v>-0.0019</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1746</v>
+        <v>-1.9623</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.5218</v>
+        <v>-0.1873</v>
       </c>
       <c r="H17" t="n">
-        <v>1.0781</v>
+        <v>-1.8971</v>
       </c>
       <c r="I17" t="n">
-        <v>-2.5998</v>
+        <v>1.7097</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.582</v>
+        <v>2.9935</v>
       </c>
       <c r="K17" t="n">
-        <v>0.8066</v>
+        <v>-1.1386</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.3887</v>
+        <v>4.1321</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9398</v>
+        <v>-3.1808</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2714</v>
+        <v>-0.7584</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.2112</v>
+        <v>-2.4223</v>
       </c>
       <c r="P17" t="n">
-        <v>0.6959</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-2.5515</v>
       </c>
       <c r="R17" t="n">
-        <v>0.6959</v>
+        <v>1.8556</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3813</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.5228</v>
+        <v>-0.4439</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1415</v>
+        <v>0.4351</v>
       </c>
       <c r="V17" t="n">
         <v>-1.0722</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. WASHINGTON</t>
+          <t>B. FERNANDO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.7562</v>
+        <v>-2.2057</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.8276</v>
+        <v>-1.1484</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.9286</v>
+        <v>-1.0573</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1873</v>
+        <v>-0.7766</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.8971</v>
+        <v>0.8127</v>
       </c>
       <c r="I18" t="n">
-        <v>1.7097</v>
+        <v>-1.5893</v>
       </c>
       <c r="J18" t="n">
-        <v>2.9935</v>
+        <v>0.6885</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.1386</v>
+        <v>0.5412</v>
       </c>
       <c r="L18" t="n">
-        <v>4.1321</v>
+        <v>0.1472</v>
       </c>
       <c r="M18" t="n">
-        <v>-3.1808</v>
+        <v>-1.4651</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7584</v>
+        <v>0.2714</v>
       </c>
       <c r="O18" t="n">
-        <v>-2.4223</v>
+        <v>-1.7365</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.6959</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q18" t="n">
         <v>-2.5515</v>
       </c>
       <c r="R18" t="n">
-        <v>1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.8008</v>
+        <v>0.1946</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.2696</v>
+        <v>-0.3576</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4687</v>
+        <v>0.5522</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X18" t="n">
         <v>-1.0722</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.4723</v>
+        <v>-3.9833</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6318</v>
+        <v>-1.0421</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.8404</v>
+        <v>-2.9412</v>
       </c>
       <c r="G19" t="n">
         <v>-4.3534</v>
@@ -1936,13 +1936,13 @@
         <v>1.1598</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.995</v>
+        <v>-0.5061</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0455</v>
+        <v>-0.4558</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0505</v>
+        <v>-0.0503</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2836</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.8941</v>
+        <v>-4.8269</v>
       </c>
       <c r="E20" t="n">
         <v>-3.9071</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.987</v>
+        <v>-0.9198</v>
       </c>
       <c r="G20" t="n">
         <v>-4.8134</v>
@@ -2014,13 +2014,13 @@
         <v>1.8556</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3084</v>
+        <v>0.3756</v>
       </c>
       <c r="T20" t="n">
         <v>0.3031</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0053</v>
+        <v>0.0725</v>
       </c>
       <c r="V20" t="n">
         <v>1.4665</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-16.0343</v>
+        <v>-16.0344</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.7728</v>
+        <v>-2.7727</v>
       </c>
       <c r="F21" t="n">
-        <v>-13.2616</v>
+        <v>-13.2617</v>
       </c>
       <c r="G21" t="n">
         <v>-14.3841</v>
@@ -2092,10 +2092,10 @@
         <v>12.7575</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8653999999999999</v>
+        <v>0.8654000000000002</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.4717</v>
+        <v>-1.4718</v>
       </c>
       <c r="U21" t="n">
         <v>2.3371</v>
